--- a/data/nasdaq100_active/구성종목_2026-06-10.xlsx
+++ b/data/nasdaq100_active/구성종목_2026-06-10.xlsx
@@ -227,7 +227,7 @@
     <t>18,002,457</t>
   </si>
   <si>
-    <t>NQM6 Index</t>
+    <t>NQM6 INDEX</t>
   </si>
   <si>
     <t>NASDAQ 100 E-MINI INDEX JUN 2026</t>
